--- a/dashboard/SwingTrade_Dashboard.xlsx
+++ b/dashboard/SwingTrade_Dashboard.xlsx
@@ -449,7 +449,7 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>25-Jul-2026 09:53 AM</t>
+          <t>25-Jul-2026 10:40 AM</t>
         </is>
       </c>
     </row>
